--- a/data/pack/eu/huevos.xlsx
+++ b/data/pack/eu/huevos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fuente y licencia" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Datos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Fuente y licencia" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K871"/>
+  <dimension ref="A1:K872"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -48339,6 +48339,61 @@
         </is>
       </c>
       <c r="K871" t="inlineStr">
+        <is>
+          <t>Source: European Commission (Agri-food data portal)</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="inlineStr">
+        <is>
+          <t>huevos</t>
+        </is>
+      </c>
+      <c r="B872" t="inlineStr">
+        <is>
+          <t>Huevos</t>
+        </is>
+      </c>
+      <c r="C872" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="D872" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="E872" t="n">
+        <v>249.16</v>
+      </c>
+      <c r="F872" t="inlineStr">
+        <is>
+          <t>100kg</t>
+        </is>
+      </c>
+      <c r="G872" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H872" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="I872" t="inlineStr">
+        <is>
+          <t>European Commission — Agri-food Data Portal (DG AGRI)</t>
+        </is>
+      </c>
+      <c r="J872" t="inlineStr">
+        <is>
+          <t>EU-REUSE-2011-833</t>
+        </is>
+      </c>
+      <c r="K872" t="inlineStr">
         <is>
           <t>Source: European Commission (Agri-food data portal)</t>
         </is>
@@ -48442,7 +48497,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -48453,7 +48508,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>870</v>
+        <v>871</v>
       </c>
     </row>
     <row r="9">
@@ -48548,7 +48603,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
